--- a/etf_holdings/2026-10-08_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00992A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.21%2,482,000</t>
+          <t>7.23%2,482,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.23%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.12%871,000</t>
+          <t>6.90%871,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.40%1,116,000</t>
+          <t>6.44%1,116,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.44%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2315</v>
+        <v>2360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.98%1,161,000</t>
+          <t>6.00%1,161,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.78%1,630,000</t>
+          <t>5.99%1,630,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>5.99%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.47%1,204,000</t>
+          <t>5.42%1,204,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11790</v>
+        <v>6660</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.94%170,000</t>
+          <t>4.48%293,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>170000</v>
+        <v>293000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6845</v>
+        <v>10615</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.45%293,000</t>
+          <t>4.48%170,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>293000</v>
+        <v>170000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.32%344,000</t>
+          <t>4.25%344,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.89%556</t>
+          <t>+1.89%135</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>556</v>
+        <v>135</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.34%2,682,000</t>
+          <t>3.38%11,420,868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2682000</v>
+        <v>11420868</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1480</v>
+        <v>557</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.23%968,000</t>
+          <t>3.33%2,682,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>968000</v>
+        <v>2682000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.33%132.5</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.33%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>132.5</v>
+        <v>1475</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.22%11,420,868</t>
+          <t>3.20%968,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>11420868</v>
+        <v>968000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.05%164,000</t>
+          <t>3.10%164,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:52</t>
+          <t>2026-10-08 23:47:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.37%185</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.04%7,245,000</t>
+          <t>2.99%7,245,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.37%3,645,000</t>
+          <t>2.56%3,645,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.36%538</t>
+          <t>-1.3%531</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.33%1,904,000</t>
+          <t>2.29%1,904,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2240</v>
+        <v>2330</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.18%429,675</t>
+          <t>2.26%422,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>429675</v>
+        <v>422000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1100</v>
+        <v>2240</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.00%844,013</t>
+          <t>2.15%429,675</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>844013</v>
+        <v>429675</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4835</v>
+        <v>1075</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.95%179,000</t>
+          <t>2.07%844,013</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>844013</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2400</v>
+        <v>4690</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.43%275,000</t>
+          <t>1.93%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>275000</v>
+        <v>179000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.27%1,000,000</t>
+          <t>1.33%1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.41%559</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>559</v>
+        <v>1965</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.26%1,000,000</t>
+          <t>0.89%200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>+1.26%806</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1990</v>
+        <v>806</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.91%200,000</t>
+          <t>0.66%373,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>200000</v>
+        <v>373000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.95%5520</t>
+          <t>+1.72%5615</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.69%51,000</t>
+          <t>0.63%51,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.14%796</t>
+          <t>-0.39%128</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>796</v>
+        <v>128</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.65%373,000</t>
+          <t>0.56%1,957,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>373000</v>
+        <v>1957000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.78%128.5</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>128.5</v>
+        <v>7165</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.55%1,957,000</t>
+          <t>0.50%33,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1957000</v>
+        <v>33000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>+4.53%877</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6805</v>
+        <v>877</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.52%33,000</t>
+          <t>0.49%261,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>33000</v>
+        <v>261000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>-1.88%1305</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17750</v>
+        <v>1305</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.46%11,000</t>
+          <t>0.46%155,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>11000</v>
+        <v>155000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:53</t>
+          <t>2026-10-08 23:47:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+5.4%839</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>839</v>
+        <v>1525</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.46%261,000</t>
+          <t>0.46%134,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>261000</v>
+        <v>134000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.37%1330</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1330</v>
+        <v>2960</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.46%155,000</t>
+          <t>0.44%63,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>155000</v>
+        <v>63000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>-0.83%297.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1535</v>
+        <v>297.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.46%134,000</t>
+          <t>0.44%659,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>134000</v>
+        <v>659000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.01%787</t>
+          <t>-1.14%778</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1720</v>
+        <v>17485</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.44%113,000</t>
+          <t>0.44%11,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>113000</v>
+        <v>11000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.33%300</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>300</v>
+        <v>1740</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.44%659,000</t>
+          <t>0.43%113,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>659000</v>
+        <v>113000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.1%989</t>
+          <t>+0.71%996</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.82%365.5</t>
+          <t>-0.68%363</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>365.5</v>
+        <v>363</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.43%508,000</t>
+          <t>0.41%508,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-0.79%1250</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3140</v>
+        <v>1250</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.41%63,000</t>
+          <t>0.28%99,952</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>63000</v>
+        <v>99952</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.4%1260</t>
+          <t>-1.84%186.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1260</v>
+        <v>186.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.28%99,952</t>
+          <t>0.27%629,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>99952</v>
+        <v>629000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:54</t>
+          <t>2026-10-08 23:47:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,102 +2944,41 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.52%190</t>
+          <t>+0.61%2465</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>190</v>
+        <v>2465</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.27%629,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>629000</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:27:54</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3131弘塑</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-3.16%2450</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-3.16%</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>2450</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-08_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:28</t>
+          <t>2026-10-08 23:53:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:29</t>
+          <t>2026-10-08 23:53:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:31</t>
+          <t>2026-10-08 23:53:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
